--- a/hourly datasets/cap_gen_year7final.xlsx
+++ b/hourly datasets/cap_gen_year7final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.0984234321627112</v>
+        <v>0.095985580911827</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1047075183849701</v>
+        <v>0.1029374317734618</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2031309505476813</v>
+        <v>0.1989230126852888</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09897717964829653</v>
+        <v>0.09555485052148066</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1974006118110077</v>
+        <v>0.1915404314333077</v>
       </c>
     </row>
     <row r="5">
@@ -531,15 +531,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07947544163689636</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+        <v>0.07531909762338543</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.004089869696999039</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15.00133567274299</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.02332725548588234</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.06729703504002842</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.08334116020674136</v>
+      </c>
       <c r="H5" t="n">
-        <v>0.1778988737996076</v>
+        <v>0.1713046785352124</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +559,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05182823082317872</v>
+        <v>0.04657458467290998</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003393416648242191</v>
+        <v>0.002594460615220291</v>
       </c>
       <c r="D6" t="n">
-        <v>10.33050640383841</v>
+        <v>9.569369589606936</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01441222100071589</v>
+        <v>0.01010335654394539</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04516837039422728</v>
+        <v>0.04148644533058955</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05848809125213079</v>
+        <v>0.05166272401523106</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1502516629858899</v>
+        <v>0.142560165584737</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +587,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05215327718220823</v>
+        <v>0.04533891767696547</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -585,7 +595,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.1505767093449194</v>
+        <v>0.1413244985887925</v>
       </c>
     </row>
     <row r="8">
@@ -595,25 +605,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0505871872593374</v>
+        <v>0.04417308600711849</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003243509853448842</v>
+        <v>0.002445450074373323</v>
       </c>
       <c r="D8" t="n">
-        <v>5.580092923639919</v>
+        <v>4.113859460860056</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01785842071342533</v>
+        <v>0.005835991824672515</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04422007702240081</v>
+        <v>0.03937654099706544</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05695429749627432</v>
+        <v>0.04896963101717069</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1490106194220486</v>
+        <v>0.1401586669189455</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +633,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05372497167157138</v>
+        <v>0.0450366640386539</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002811005531344026</v>
+        <v>0.001769461171736624</v>
       </c>
       <c r="D9" t="n">
-        <v>4.618073889692631</v>
+        <v>3.142961585406661</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01395161275276387</v>
+        <v>0.004108679278498041</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04821209580664321</v>
+        <v>0.04156770371972607</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05923784753650124</v>
+        <v>0.04850562435757997</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1521484038342826</v>
+        <v>0.1410222449504809</v>
       </c>
     </row>
     <row r="10">
@@ -651,15 +661,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0558167460178016</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+        <v>0.04633612938515087</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001496102859082277</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.565927160998005</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.003651764599911244</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.04340331846052296</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.04926894030977909</v>
+      </c>
       <c r="H10" t="n">
-        <v>0.1542401781805128</v>
+        <v>0.1423217102969779</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +689,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02845956604289967</v>
+        <v>0.02799883078731313</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -677,7 +697,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1268829982056109</v>
+        <v>0.1239844116991401</v>
       </c>
     </row>
     <row r="12">
@@ -687,7 +707,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04965314735332428</v>
+        <v>0.04850290989295106</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -695,7 +715,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1480765795160355</v>
+        <v>0.1444884908047781</v>
       </c>
     </row>
     <row r="13">
@@ -705,7 +725,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06373438030096099</v>
+        <v>0.06108934331317046</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -713,7 +733,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1621578124636722</v>
+        <v>0.1570749242249975</v>
       </c>
     </row>
     <row r="14">
@@ -723,7 +743,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07104767068378057</v>
+        <v>0.06936121019049994</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -731,7 +751,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1694711028464918</v>
+        <v>0.1653467911023269</v>
       </c>
     </row>
     <row r="15">
@@ -741,7 +761,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07553372761543573</v>
+        <v>0.07390522181581038</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -749,7 +769,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1739571597781469</v>
+        <v>0.1698908027276374</v>
       </c>
     </row>
     <row r="16">
@@ -759,7 +779,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07990381851884359</v>
+        <v>0.07739348808299194</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -767,7 +787,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1783272506815548</v>
+        <v>0.1733790689948189</v>
       </c>
     </row>
     <row r="17">
@@ -777,7 +797,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08282733730190932</v>
+        <v>0.08016864762836388</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -785,7 +805,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1812507694646205</v>
+        <v>0.1761542285401909</v>
       </c>
     </row>
     <row r="18">
@@ -795,22 +815,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.0984234321627112</v>
+        <v>-0.095985580911827</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01068438068956193</v>
+        <v>0.009925185074246229</v>
       </c>
       <c r="D18" t="n">
-        <v>-17.27768835861711</v>
+        <v>-17.31358842852945</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04626682776618744</v>
+        <v>0.04282641952420323</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1194315750007144</v>
+        <v>-0.1154914315898203</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.07741528932470813</v>
+        <v>-0.07647973023383368</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -823,7 +843,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08587118883494811</v>
+        <v>0.08296425672146143</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -831,7 +851,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1842946209976593</v>
+        <v>0.1789498376332884</v>
       </c>
     </row>
     <row r="20">
@@ -841,7 +861,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08633252247960442</v>
+        <v>0.08370536269544183</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -849,7 +869,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1847559546423156</v>
+        <v>0.1796909436072688</v>
       </c>
     </row>
     <row r="21">
@@ -859,7 +879,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0927173209213141</v>
+        <v>0.08942762021361561</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -867,7 +887,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1911407530840253</v>
+        <v>0.1854132011254426</v>
       </c>
     </row>
     <row r="22">
@@ -877,7 +897,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.09534766610739499</v>
+        <v>0.0929947323077176</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -885,7 +905,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.1937710982701062</v>
+        <v>0.1889803132195446</v>
       </c>
     </row>
     <row r="23">
@@ -895,7 +915,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.09838714458859858</v>
+        <v>0.09637920924605145</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -903,7 +923,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.1968105767513098</v>
+        <v>0.1923647901578784</v>
       </c>
     </row>
     <row r="24">
@@ -913,25 +933,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1013695941648085</v>
+        <v>0.1004968973721191</v>
       </c>
       <c r="C24" t="n">
-        <v>0.008373327976158184</v>
+        <v>0.007871626039040324</v>
       </c>
       <c r="D24" t="n">
-        <v>20.72497380922693</v>
+        <v>20.95791246725275</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05754622721266231</v>
+        <v>0.05430909003811169</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08490022277718361</v>
+        <v>0.0850198624846297</v>
       </c>
       <c r="G24" t="n">
-        <v>0.117838965552433</v>
+        <v>0.1159739322596081</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1997930263275197</v>
+        <v>0.1964824782839461</v>
       </c>
     </row>
     <row r="25">
@@ -941,25 +961,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.101888784563982</v>
+        <v>0.1001574673548079</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008371035866017383</v>
+        <v>0.00786054468314621</v>
       </c>
       <c r="D25" t="n">
-        <v>20.46220124530411</v>
+        <v>20.65070108913503</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05954346281266894</v>
+        <v>0.05770972918647265</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08542163044845742</v>
+        <v>0.08469952347062953</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1183559386795065</v>
+        <v>0.1156154112389863</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2003122167266932</v>
+        <v>0.1961430482666349</v>
       </c>
     </row>
     <row r="26">
@@ -969,25 +989,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1035065334072906</v>
+        <v>0.1024651578055013</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008286485437668741</v>
+        <v>0.007731724353376552</v>
       </c>
       <c r="D26" t="n">
-        <v>20.26555869680995</v>
+        <v>20.51312592078147</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06571045960041402</v>
+        <v>0.06207533662104989</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08720476725378171</v>
+        <v>0.08726117000413212</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1198082995607995</v>
+        <v>0.1176691456068699</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2019299655700018</v>
+        <v>0.1984507387173283</v>
       </c>
     </row>
     <row r="27">
@@ -997,25 +1017,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.110136090607751</v>
+        <v>0.1091271799192364</v>
       </c>
       <c r="C27" t="n">
-        <v>0.008484351742612996</v>
+        <v>0.00792572663377474</v>
       </c>
       <c r="D27" t="n">
-        <v>19.94007017008146</v>
+        <v>20.20727317841305</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0676018973312657</v>
+        <v>0.06303860073983854</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09344886607715885</v>
+        <v>0.09354435955610885</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1268233151383435</v>
+        <v>0.1247100002823642</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2085595227704622</v>
+        <v>0.2051127608310634</v>
       </c>
     </row>
     <row r="28">
@@ -1025,25 +1045,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1107059510211285</v>
+        <v>0.1096510740090393</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0082153362048246</v>
+        <v>0.007444674629831696</v>
       </c>
       <c r="D28" t="n">
-        <v>19.91213547012392</v>
+        <v>20.47369862183459</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08362679391497141</v>
+        <v>0.07847340313856502</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0945506648204571</v>
+        <v>0.09501793875380302</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1268612372218009</v>
+        <v>0.1242842092642755</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2091293831838397</v>
+        <v>0.2056366549208663</v>
       </c>
     </row>
     <row r="29">
@@ -1053,25 +1073,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.05551354628186445</v>
+        <v>0.04469570720298193</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00367589659326651</v>
+        <v>0.002434540259020099</v>
       </c>
       <c r="D29" t="n">
-        <v>4.452279470895774</v>
+        <v>2.585164022131984</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0058356924756495</v>
+        <v>0.004978197792131846</v>
       </c>
       <c r="F29" t="n">
-        <v>0.04829476130608929</v>
+        <v>0.03991883610721246</v>
       </c>
       <c r="G29" t="n">
-        <v>0.06273233125763926</v>
+        <v>0.04947257829875277</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1539369784445757</v>
+        <v>0.1406812881148089</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year7final.xlsx
+++ b/hourly datasets/cap_gen_year7final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2173505279977869</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.095985580911827</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.09135272580887446</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1029374317734618</v>
+        <v>0.3767818311512596</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1989230126852888</v>
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2507840289623472</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09555485052148066</v>
+        <v>0.3729365991487697</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1915404314333077</v>
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2469387969598573</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +545,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07531909762338543</v>
+        <v>0.3933522497952588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004089869696999039</v>
+        <v>0.004737294501496768</v>
       </c>
       <c r="D5" t="n">
-        <v>15.00133567274299</v>
+        <v>20.80185784765329</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02332725548588234</v>
+        <v>0.02396933163946575</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06729703504002842</v>
+        <v>0.08142482700962689</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08334116020674136</v>
+        <v>0.1000090686713846</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1713046785352124</v>
+        <v>8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2673544476063464</v>
       </c>
     </row>
     <row r="6">
@@ -559,25 +576,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04657458467290998</v>
+        <v>0.3856781764619027</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002594460615220291</v>
+        <v>0.003187877084608467</v>
       </c>
       <c r="D6" t="n">
-        <v>9.569369589606936</v>
+        <v>16.90491325031164</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01010335654394539</v>
+        <v>0.01023728325309703</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04148644533058955</v>
+        <v>0.05411396835807684</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05166272401523106</v>
+        <v>0.06661912611402067</v>
       </c>
       <c r="H6" t="n">
-        <v>0.142560165584737</v>
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2596803742729903</v>
       </c>
     </row>
     <row r="7">
@@ -587,7 +607,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04533891767696547</v>
+        <v>0.6055647640872293</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -595,7 +615,10 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.1413244985887925</v>
+        <v>23</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.4795669618983168</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +628,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04417308600711849</v>
+        <v>0.6268342679206239</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002445450074373323</v>
+        <v>0.01725168776343831</v>
       </c>
       <c r="D8" t="n">
-        <v>4.113859460860056</v>
+        <v>26.50735383353378</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005835991824672515</v>
+        <v>0.006093649318546803</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03937654099706544</v>
+        <v>0.4066026195528661</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04896963101717069</v>
+        <v>0.4742440613077786</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1401586669189455</v>
+        <v>23</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5008364657317115</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +659,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0450366640386539</v>
+        <v>0.6451324251801174</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001769461171736624</v>
+        <v>0.01521223713887705</v>
       </c>
       <c r="D9" t="n">
-        <v>3.142961585406661</v>
+        <v>30.0902527246251</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004108679278498041</v>
+        <v>0.004311263305240071</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04156770371972607</v>
+        <v>0.4345355349027989</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04850562435757997</v>
+        <v>0.4941758190676748</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1410222449504809</v>
+        <v>23</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5191346229912049</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +690,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04633612938515087</v>
+        <v>0.6826080749873069</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001496102859082277</v>
+        <v>0.01371421442672563</v>
       </c>
       <c r="D10" t="n">
-        <v>3.565927160998005</v>
+        <v>35.88492774354862</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003651764599911244</v>
+        <v>0.003821068665555164</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04340331846052296</v>
+        <v>0.4745085260206919</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04926894030977909</v>
+        <v>0.5282751968934062</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1423217102969779</v>
+        <v>23</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5566102727983945</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +721,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02799883078731313</v>
+        <v>0.2599102476668708</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +729,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1239844116991401</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1339124454779584</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +742,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04850290989295106</v>
+        <v>0.2852074170404186</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +750,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1444884908047781</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1592096148515061</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +763,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06108934331317046</v>
+        <v>0.301243821478502</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +771,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1570749242249975</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1752460192895896</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +784,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06936121019049994</v>
+        <v>0.3100602065095728</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -751,7 +792,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1653467911023269</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1840624043206603</v>
       </c>
     </row>
     <row r="15">
@@ -761,7 +805,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07390522181581038</v>
+        <v>0.3174365342211667</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -769,7 +813,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1698908027276374</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1914387320322543</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +826,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07739348808299194</v>
+        <v>0.3230758126986247</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -787,7 +834,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1733790689948189</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1970780105097123</v>
       </c>
     </row>
     <row r="17">
@@ -797,7 +847,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08016864762836388</v>
+        <v>0.3268261698236987</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -805,7 +855,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1761542285401909</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2008283676347863</v>
       </c>
     </row>
     <row r="18">
@@ -815,24 +868,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.095985580911827</v>
+        <v>0.1259978021889124</v>
       </c>
       <c r="C18" t="n">
-        <v>0.009925185074246229</v>
+        <v>0.009732644160126957</v>
       </c>
       <c r="D18" t="n">
-        <v>-17.31358842852945</v>
+        <v>-17.18654224979414</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04282641952420323</v>
+        <v>0.04256545476104786</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1154914315898203</v>
+        <v>-0.1136241114473833</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.07647973023383368</v>
+        <v>-0.07536916351425897</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -843,7 +899,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08296425672146143</v>
+        <v>0.3304008885367393</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -851,7 +907,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1789498376332884</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2044030863478268</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +920,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08370536269544183</v>
+        <v>0.3324137802671652</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -869,7 +928,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1796909436072688</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2064159780782527</v>
       </c>
     </row>
     <row r="21">
@@ -879,7 +941,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.08942762021361561</v>
+        <v>0.3361224848655268</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -887,7 +949,10 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1854132011254426</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2101246826766144</v>
       </c>
     </row>
     <row r="22">
@@ -897,7 +962,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0929947323077176</v>
+        <v>0.3411590178661466</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -905,7 +970,10 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.1889803132195446</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2151612156772341</v>
       </c>
     </row>
     <row r="23">
@@ -915,7 +983,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.09637920924605145</v>
+        <v>0.3450084737864073</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -923,7 +991,10 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.1923647901578784</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2190106715974948</v>
       </c>
     </row>
     <row r="24">
@@ -933,25 +1004,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1004968973721191</v>
+        <v>0.3528440765522803</v>
       </c>
       <c r="C24" t="n">
-        <v>0.007871626039040324</v>
+        <v>0.007827004087389844</v>
       </c>
       <c r="D24" t="n">
-        <v>20.95791246725275</v>
+        <v>20.89344303589129</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05430909003811169</v>
+        <v>0.0542264385105776</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0850198624846297</v>
+        <v>0.0846175619164042</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1159739322596081</v>
+        <v>0.1153960954817422</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1964824782839461</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2268462743633679</v>
       </c>
     </row>
     <row r="25">
@@ -961,25 +1035,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1001574673548079</v>
+        <v>0.3554152464696297</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00786054468314621</v>
+        <v>0.007806255952395876</v>
       </c>
       <c r="D25" t="n">
-        <v>20.65070108913503</v>
+        <v>20.57774174092365</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05770972918647265</v>
+        <v>0.05742876925241427</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08469952347062953</v>
+        <v>0.08424834900106723</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1156154112389863</v>
+        <v>0.1149506868173086</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1961430482666349</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2294174442807173</v>
       </c>
     </row>
     <row r="26">
@@ -989,25 +1066,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1024651578055013</v>
+        <v>0.3601958375863335</v>
       </c>
       <c r="C26" t="n">
-        <v>0.007731724353376552</v>
+        <v>0.00766157726061728</v>
       </c>
       <c r="D26" t="n">
-        <v>20.51312592078147</v>
+        <v>20.41950111904823</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06207533662104989</v>
+        <v>0.06171184315221956</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08726117000413212</v>
+        <v>0.08671738044114168</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1176691456068699</v>
+        <v>0.1168491146851643</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1984507387173283</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2341980353974211</v>
       </c>
     </row>
     <row r="27">
@@ -1017,25 +1097,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1091271799192364</v>
+        <v>0.3644370261118007</v>
       </c>
       <c r="C27" t="n">
-        <v>0.00792572663377474</v>
+        <v>0.007762685453924285</v>
       </c>
       <c r="D27" t="n">
-        <v>20.20727317841305</v>
+        <v>20.0325526473552</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06303860073983854</v>
+        <v>0.06235803180340559</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09354435955610885</v>
+        <v>0.09224090658037171</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1247100002823642</v>
+        <v>0.1227652447761998</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2051127608310634</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2384392239228882</v>
       </c>
     </row>
     <row r="28">
@@ -1045,25 +1128,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1096510740090393</v>
+        <v>0.3675442579839218</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007444674629831696</v>
+        <v>0.007337093564070294</v>
       </c>
       <c r="D28" t="n">
-        <v>20.47369862183459</v>
+        <v>20.30055003385446</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07847340313856502</v>
+        <v>0.07756027327369053</v>
       </c>
       <c r="F28" t="n">
-        <v>0.09501793875380302</v>
+        <v>0.09381650141351278</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1242842092642755</v>
+        <v>0.1226597615335411</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2056366549208663</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2415464557950093</v>
       </c>
     </row>
     <row r="29">
@@ -1073,25 +1159,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.04469570720298193</v>
+        <v>0.650808778915087</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002434540259020099</v>
+        <v>0.02396765466442012</v>
       </c>
       <c r="D29" t="n">
-        <v>2.585164022131984</v>
+        <v>19.18317644479792</v>
       </c>
       <c r="E29" t="n">
-        <v>0.004978197792131846</v>
+        <v>0.005608590013924943</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03991883610721246</v>
+        <v>0.4188657745050102</v>
       </c>
       <c r="G29" t="n">
-        <v>0.04947257829875277</v>
+        <v>0.5128402138561129</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1406812881148089</v>
+        <v>23</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.5248109767261746</v>
       </c>
     </row>
   </sheetData>
